--- a/studies/Eichkamp/rye_mfa_results_v1.xlsx
+++ b/studies/Eichkamp/rye_mfa_results_v1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="32">
   <si>
     <t>Flow_ID</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>S_7</t>
+  </si>
+  <si>
+    <t>dS_8</t>
+  </si>
+  <si>
+    <t>S_8</t>
   </si>
 </sst>
 </file>
@@ -38292,7 +38298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1009"/>
+  <dimension ref="A1:F1261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -58475,6 +58481,5046 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1010" spans="1:6">
+      <c r="A1010" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1010">
+        <v>1920</v>
+      </c>
+      <c r="C1010">
+        <v>0</v>
+      </c>
+      <c r="D1010">
+        <v>0</v>
+      </c>
+      <c r="E1010">
+        <v>0</v>
+      </c>
+      <c r="F1010">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:6">
+      <c r="A1011" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1011">
+        <v>1921</v>
+      </c>
+      <c r="C1011">
+        <v>0</v>
+      </c>
+      <c r="D1011">
+        <v>0</v>
+      </c>
+      <c r="E1011">
+        <v>0</v>
+      </c>
+      <c r="F1011">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:6">
+      <c r="A1012" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1012">
+        <v>1922</v>
+      </c>
+      <c r="C1012">
+        <v>0</v>
+      </c>
+      <c r="D1012">
+        <v>0</v>
+      </c>
+      <c r="E1012">
+        <v>0</v>
+      </c>
+      <c r="F1012">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:6">
+      <c r="A1013" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1013">
+        <v>1923</v>
+      </c>
+      <c r="C1013">
+        <v>0</v>
+      </c>
+      <c r="D1013">
+        <v>0</v>
+      </c>
+      <c r="E1013">
+        <v>0</v>
+      </c>
+      <c r="F1013">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:6">
+      <c r="A1014" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1014">
+        <v>1924</v>
+      </c>
+      <c r="C1014">
+        <v>0</v>
+      </c>
+      <c r="D1014">
+        <v>0</v>
+      </c>
+      <c r="E1014">
+        <v>0</v>
+      </c>
+      <c r="F1014">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:6">
+      <c r="A1015" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1015">
+        <v>1925</v>
+      </c>
+      <c r="C1015">
+        <v>0</v>
+      </c>
+      <c r="D1015">
+        <v>0</v>
+      </c>
+      <c r="E1015">
+        <v>0</v>
+      </c>
+      <c r="F1015">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:6">
+      <c r="A1016" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1016">
+        <v>1926</v>
+      </c>
+      <c r="C1016">
+        <v>0</v>
+      </c>
+      <c r="D1016">
+        <v>0</v>
+      </c>
+      <c r="E1016">
+        <v>0</v>
+      </c>
+      <c r="F1016">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:6">
+      <c r="A1017" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1017">
+        <v>1927</v>
+      </c>
+      <c r="C1017">
+        <v>0</v>
+      </c>
+      <c r="D1017">
+        <v>0</v>
+      </c>
+      <c r="E1017">
+        <v>0</v>
+      </c>
+      <c r="F1017">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:6">
+      <c r="A1018" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1018">
+        <v>1928</v>
+      </c>
+      <c r="C1018">
+        <v>0</v>
+      </c>
+      <c r="D1018">
+        <v>0</v>
+      </c>
+      <c r="E1018">
+        <v>0</v>
+      </c>
+      <c r="F1018">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:6">
+      <c r="A1019" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1019">
+        <v>1929</v>
+      </c>
+      <c r="C1019">
+        <v>0</v>
+      </c>
+      <c r="D1019">
+        <v>0</v>
+      </c>
+      <c r="E1019">
+        <v>0</v>
+      </c>
+      <c r="F1019">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:6">
+      <c r="A1020" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1020">
+        <v>1930</v>
+      </c>
+      <c r="C1020">
+        <v>0</v>
+      </c>
+      <c r="D1020">
+        <v>0</v>
+      </c>
+      <c r="E1020">
+        <v>0</v>
+      </c>
+      <c r="F1020">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:6">
+      <c r="A1021" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1021">
+        <v>1931</v>
+      </c>
+      <c r="C1021">
+        <v>0</v>
+      </c>
+      <c r="D1021">
+        <v>0</v>
+      </c>
+      <c r="E1021">
+        <v>0</v>
+      </c>
+      <c r="F1021">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:6">
+      <c r="A1022" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1022">
+        <v>1932</v>
+      </c>
+      <c r="C1022">
+        <v>0</v>
+      </c>
+      <c r="D1022">
+        <v>0</v>
+      </c>
+      <c r="E1022">
+        <v>0</v>
+      </c>
+      <c r="F1022">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:6">
+      <c r="A1023" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1023">
+        <v>1933</v>
+      </c>
+      <c r="C1023">
+        <v>0</v>
+      </c>
+      <c r="D1023">
+        <v>0</v>
+      </c>
+      <c r="E1023">
+        <v>0</v>
+      </c>
+      <c r="F1023">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:6">
+      <c r="A1024" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1024">
+        <v>1934</v>
+      </c>
+      <c r="C1024">
+        <v>0</v>
+      </c>
+      <c r="D1024">
+        <v>0</v>
+      </c>
+      <c r="E1024">
+        <v>0</v>
+      </c>
+      <c r="F1024">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:6">
+      <c r="A1025" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1025">
+        <v>1935</v>
+      </c>
+      <c r="C1025">
+        <v>0</v>
+      </c>
+      <c r="D1025">
+        <v>0</v>
+      </c>
+      <c r="E1025">
+        <v>0</v>
+      </c>
+      <c r="F1025">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:6">
+      <c r="A1026" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1026">
+        <v>1936</v>
+      </c>
+      <c r="C1026">
+        <v>0</v>
+      </c>
+      <c r="D1026">
+        <v>0</v>
+      </c>
+      <c r="E1026">
+        <v>0</v>
+      </c>
+      <c r="F1026">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:6">
+      <c r="A1027" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1027">
+        <v>1937</v>
+      </c>
+      <c r="C1027">
+        <v>0</v>
+      </c>
+      <c r="D1027">
+        <v>0</v>
+      </c>
+      <c r="E1027">
+        <v>0</v>
+      </c>
+      <c r="F1027">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:6">
+      <c r="A1028" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1028">
+        <v>1938</v>
+      </c>
+      <c r="C1028">
+        <v>0</v>
+      </c>
+      <c r="D1028">
+        <v>0</v>
+      </c>
+      <c r="E1028">
+        <v>0</v>
+      </c>
+      <c r="F1028">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:6">
+      <c r="A1029" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1029">
+        <v>1939</v>
+      </c>
+      <c r="C1029">
+        <v>0</v>
+      </c>
+      <c r="D1029">
+        <v>0</v>
+      </c>
+      <c r="E1029">
+        <v>0</v>
+      </c>
+      <c r="F1029">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:6">
+      <c r="A1030" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1030">
+        <v>1940</v>
+      </c>
+      <c r="C1030">
+        <v>0</v>
+      </c>
+      <c r="D1030">
+        <v>0</v>
+      </c>
+      <c r="E1030">
+        <v>0</v>
+      </c>
+      <c r="F1030">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:6">
+      <c r="A1031" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1031">
+        <v>1941</v>
+      </c>
+      <c r="C1031">
+        <v>0</v>
+      </c>
+      <c r="D1031">
+        <v>0</v>
+      </c>
+      <c r="E1031">
+        <v>0</v>
+      </c>
+      <c r="F1031">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:6">
+      <c r="A1032" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1032">
+        <v>1942</v>
+      </c>
+      <c r="C1032">
+        <v>0</v>
+      </c>
+      <c r="D1032">
+        <v>0</v>
+      </c>
+      <c r="E1032">
+        <v>0</v>
+      </c>
+      <c r="F1032">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:6">
+      <c r="A1033" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1033">
+        <v>1943</v>
+      </c>
+      <c r="C1033">
+        <v>0</v>
+      </c>
+      <c r="D1033">
+        <v>0</v>
+      </c>
+      <c r="E1033">
+        <v>0</v>
+      </c>
+      <c r="F1033">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:6">
+      <c r="A1034" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1034">
+        <v>1944</v>
+      </c>
+      <c r="C1034">
+        <v>0</v>
+      </c>
+      <c r="D1034">
+        <v>0</v>
+      </c>
+      <c r="E1034">
+        <v>0</v>
+      </c>
+      <c r="F1034">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:6">
+      <c r="A1035" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1035">
+        <v>1945</v>
+      </c>
+      <c r="C1035">
+        <v>0</v>
+      </c>
+      <c r="D1035">
+        <v>0</v>
+      </c>
+      <c r="E1035">
+        <v>0</v>
+      </c>
+      <c r="F1035">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:6">
+      <c r="A1036" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1036">
+        <v>1946</v>
+      </c>
+      <c r="C1036">
+        <v>0</v>
+      </c>
+      <c r="D1036">
+        <v>0</v>
+      </c>
+      <c r="E1036">
+        <v>0</v>
+      </c>
+      <c r="F1036">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:6">
+      <c r="A1037" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1037">
+        <v>1947</v>
+      </c>
+      <c r="C1037">
+        <v>0</v>
+      </c>
+      <c r="D1037">
+        <v>0</v>
+      </c>
+      <c r="E1037">
+        <v>0</v>
+      </c>
+      <c r="F1037">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:6">
+      <c r="A1038" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1038">
+        <v>1948</v>
+      </c>
+      <c r="C1038">
+        <v>0</v>
+      </c>
+      <c r="D1038">
+        <v>0</v>
+      </c>
+      <c r="E1038">
+        <v>0</v>
+      </c>
+      <c r="F1038">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:6">
+      <c r="A1039" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1039">
+        <v>1949</v>
+      </c>
+      <c r="C1039">
+        <v>0</v>
+      </c>
+      <c r="D1039">
+        <v>0</v>
+      </c>
+      <c r="E1039">
+        <v>0</v>
+      </c>
+      <c r="F1039">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:6">
+      <c r="A1040" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1040">
+        <v>1950</v>
+      </c>
+      <c r="C1040">
+        <v>0</v>
+      </c>
+      <c r="D1040">
+        <v>0</v>
+      </c>
+      <c r="E1040">
+        <v>0</v>
+      </c>
+      <c r="F1040">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:6">
+      <c r="A1041" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1041">
+        <v>1951</v>
+      </c>
+      <c r="C1041">
+        <v>0</v>
+      </c>
+      <c r="D1041">
+        <v>0</v>
+      </c>
+      <c r="E1041">
+        <v>0</v>
+      </c>
+      <c r="F1041">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:6">
+      <c r="A1042" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1042">
+        <v>1952</v>
+      </c>
+      <c r="C1042">
+        <v>0</v>
+      </c>
+      <c r="D1042">
+        <v>0</v>
+      </c>
+      <c r="E1042">
+        <v>0</v>
+      </c>
+      <c r="F1042">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:6">
+      <c r="A1043" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1043">
+        <v>1953</v>
+      </c>
+      <c r="C1043">
+        <v>0</v>
+      </c>
+      <c r="D1043">
+        <v>0</v>
+      </c>
+      <c r="E1043">
+        <v>0</v>
+      </c>
+      <c r="F1043">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:6">
+      <c r="A1044" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1044">
+        <v>1954</v>
+      </c>
+      <c r="C1044">
+        <v>0</v>
+      </c>
+      <c r="D1044">
+        <v>0</v>
+      </c>
+      <c r="E1044">
+        <v>0</v>
+      </c>
+      <c r="F1044">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:6">
+      <c r="A1045" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1045">
+        <v>1955</v>
+      </c>
+      <c r="C1045">
+        <v>0</v>
+      </c>
+      <c r="D1045">
+        <v>0</v>
+      </c>
+      <c r="E1045">
+        <v>0</v>
+      </c>
+      <c r="F1045">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:6">
+      <c r="A1046" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1046">
+        <v>1956</v>
+      </c>
+      <c r="C1046">
+        <v>0</v>
+      </c>
+      <c r="D1046">
+        <v>0</v>
+      </c>
+      <c r="E1046">
+        <v>0</v>
+      </c>
+      <c r="F1046">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:6">
+      <c r="A1047" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1047">
+        <v>1957</v>
+      </c>
+      <c r="C1047">
+        <v>0</v>
+      </c>
+      <c r="D1047">
+        <v>0</v>
+      </c>
+      <c r="E1047">
+        <v>0</v>
+      </c>
+      <c r="F1047">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:6">
+      <c r="A1048" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1048">
+        <v>1958</v>
+      </c>
+      <c r="C1048">
+        <v>0</v>
+      </c>
+      <c r="D1048">
+        <v>0</v>
+      </c>
+      <c r="E1048">
+        <v>0</v>
+      </c>
+      <c r="F1048">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:6">
+      <c r="A1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1049">
+        <v>1959</v>
+      </c>
+      <c r="C1049">
+        <v>0</v>
+      </c>
+      <c r="D1049">
+        <v>0</v>
+      </c>
+      <c r="E1049">
+        <v>0</v>
+      </c>
+      <c r="F1049">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:6">
+      <c r="A1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1050">
+        <v>1960</v>
+      </c>
+      <c r="C1050">
+        <v>0</v>
+      </c>
+      <c r="D1050">
+        <v>0</v>
+      </c>
+      <c r="E1050">
+        <v>0</v>
+      </c>
+      <c r="F1050">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:6">
+      <c r="A1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1051">
+        <v>1961</v>
+      </c>
+      <c r="C1051">
+        <v>0</v>
+      </c>
+      <c r="D1051">
+        <v>0</v>
+      </c>
+      <c r="E1051">
+        <v>0</v>
+      </c>
+      <c r="F1051">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:6">
+      <c r="A1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1052">
+        <v>1962</v>
+      </c>
+      <c r="C1052">
+        <v>0</v>
+      </c>
+      <c r="D1052">
+        <v>0</v>
+      </c>
+      <c r="E1052">
+        <v>0</v>
+      </c>
+      <c r="F1052">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:6">
+      <c r="A1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1053">
+        <v>1963</v>
+      </c>
+      <c r="C1053">
+        <v>0</v>
+      </c>
+      <c r="D1053">
+        <v>0</v>
+      </c>
+      <c r="E1053">
+        <v>0</v>
+      </c>
+      <c r="F1053">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:6">
+      <c r="A1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1054">
+        <v>1964</v>
+      </c>
+      <c r="C1054">
+        <v>0</v>
+      </c>
+      <c r="D1054">
+        <v>0</v>
+      </c>
+      <c r="E1054">
+        <v>0</v>
+      </c>
+      <c r="F1054">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:6">
+      <c r="A1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1055">
+        <v>1965</v>
+      </c>
+      <c r="C1055">
+        <v>0</v>
+      </c>
+      <c r="D1055">
+        <v>0</v>
+      </c>
+      <c r="E1055">
+        <v>0</v>
+      </c>
+      <c r="F1055">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:6">
+      <c r="A1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1056">
+        <v>1966</v>
+      </c>
+      <c r="C1056">
+        <v>0</v>
+      </c>
+      <c r="D1056">
+        <v>0</v>
+      </c>
+      <c r="E1056">
+        <v>0</v>
+      </c>
+      <c r="F1056">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:6">
+      <c r="A1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1057">
+        <v>1967</v>
+      </c>
+      <c r="C1057">
+        <v>0</v>
+      </c>
+      <c r="D1057">
+        <v>0</v>
+      </c>
+      <c r="E1057">
+        <v>0</v>
+      </c>
+      <c r="F1057">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:6">
+      <c r="A1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1058">
+        <v>1968</v>
+      </c>
+      <c r="C1058">
+        <v>0</v>
+      </c>
+      <c r="D1058">
+        <v>0</v>
+      </c>
+      <c r="E1058">
+        <v>0</v>
+      </c>
+      <c r="F1058">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:6">
+      <c r="A1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1059">
+        <v>1969</v>
+      </c>
+      <c r="C1059">
+        <v>0</v>
+      </c>
+      <c r="D1059">
+        <v>0</v>
+      </c>
+      <c r="E1059">
+        <v>0</v>
+      </c>
+      <c r="F1059">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:6">
+      <c r="A1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1060">
+        <v>1970</v>
+      </c>
+      <c r="C1060">
+        <v>0</v>
+      </c>
+      <c r="D1060">
+        <v>0</v>
+      </c>
+      <c r="E1060">
+        <v>0</v>
+      </c>
+      <c r="F1060">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:6">
+      <c r="A1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1061">
+        <v>1971</v>
+      </c>
+      <c r="C1061">
+        <v>0</v>
+      </c>
+      <c r="D1061">
+        <v>0</v>
+      </c>
+      <c r="E1061">
+        <v>0</v>
+      </c>
+      <c r="F1061">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:6">
+      <c r="A1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1062">
+        <v>1972</v>
+      </c>
+      <c r="C1062">
+        <v>0</v>
+      </c>
+      <c r="D1062">
+        <v>0</v>
+      </c>
+      <c r="E1062">
+        <v>0</v>
+      </c>
+      <c r="F1062">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:6">
+      <c r="A1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1063">
+        <v>1973</v>
+      </c>
+      <c r="C1063">
+        <v>0</v>
+      </c>
+      <c r="D1063">
+        <v>0</v>
+      </c>
+      <c r="E1063">
+        <v>0</v>
+      </c>
+      <c r="F1063">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:6">
+      <c r="A1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1064">
+        <v>1974</v>
+      </c>
+      <c r="C1064">
+        <v>0</v>
+      </c>
+      <c r="D1064">
+        <v>0</v>
+      </c>
+      <c r="E1064">
+        <v>0</v>
+      </c>
+      <c r="F1064">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:6">
+      <c r="A1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1065">
+        <v>1975</v>
+      </c>
+      <c r="C1065">
+        <v>0</v>
+      </c>
+      <c r="D1065">
+        <v>0</v>
+      </c>
+      <c r="E1065">
+        <v>0</v>
+      </c>
+      <c r="F1065">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:6">
+      <c r="A1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1066">
+        <v>1976</v>
+      </c>
+      <c r="C1066">
+        <v>0</v>
+      </c>
+      <c r="D1066">
+        <v>0</v>
+      </c>
+      <c r="E1066">
+        <v>0</v>
+      </c>
+      <c r="F1066">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:6">
+      <c r="A1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1067">
+        <v>1977</v>
+      </c>
+      <c r="C1067">
+        <v>0</v>
+      </c>
+      <c r="D1067">
+        <v>0</v>
+      </c>
+      <c r="E1067">
+        <v>0</v>
+      </c>
+      <c r="F1067">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:6">
+      <c r="A1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1068">
+        <v>1978</v>
+      </c>
+      <c r="C1068">
+        <v>0</v>
+      </c>
+      <c r="D1068">
+        <v>0</v>
+      </c>
+      <c r="E1068">
+        <v>0</v>
+      </c>
+      <c r="F1068">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:6">
+      <c r="A1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1069">
+        <v>1979</v>
+      </c>
+      <c r="C1069">
+        <v>0</v>
+      </c>
+      <c r="D1069">
+        <v>0</v>
+      </c>
+      <c r="E1069">
+        <v>0</v>
+      </c>
+      <c r="F1069">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:6">
+      <c r="A1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1070">
+        <v>1980</v>
+      </c>
+      <c r="C1070">
+        <v>0</v>
+      </c>
+      <c r="D1070">
+        <v>0</v>
+      </c>
+      <c r="E1070">
+        <v>0</v>
+      </c>
+      <c r="F1070">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:6">
+      <c r="A1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1071">
+        <v>1981</v>
+      </c>
+      <c r="C1071">
+        <v>0</v>
+      </c>
+      <c r="D1071">
+        <v>0</v>
+      </c>
+      <c r="E1071">
+        <v>0</v>
+      </c>
+      <c r="F1071">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:6">
+      <c r="A1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1072">
+        <v>1982</v>
+      </c>
+      <c r="C1072">
+        <v>0</v>
+      </c>
+      <c r="D1072">
+        <v>0</v>
+      </c>
+      <c r="E1072">
+        <v>0</v>
+      </c>
+      <c r="F1072">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:6">
+      <c r="A1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1073">
+        <v>1983</v>
+      </c>
+      <c r="C1073">
+        <v>0</v>
+      </c>
+      <c r="D1073">
+        <v>0</v>
+      </c>
+      <c r="E1073">
+        <v>0</v>
+      </c>
+      <c r="F1073">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:6">
+      <c r="A1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1074">
+        <v>1984</v>
+      </c>
+      <c r="C1074">
+        <v>0</v>
+      </c>
+      <c r="D1074">
+        <v>0</v>
+      </c>
+      <c r="E1074">
+        <v>0</v>
+      </c>
+      <c r="F1074">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:6">
+      <c r="A1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1075">
+        <v>1985</v>
+      </c>
+      <c r="C1075">
+        <v>0</v>
+      </c>
+      <c r="D1075">
+        <v>0</v>
+      </c>
+      <c r="E1075">
+        <v>0</v>
+      </c>
+      <c r="F1075">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:6">
+      <c r="A1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1076">
+        <v>1986</v>
+      </c>
+      <c r="C1076">
+        <v>0</v>
+      </c>
+      <c r="D1076">
+        <v>0</v>
+      </c>
+      <c r="E1076">
+        <v>0</v>
+      </c>
+      <c r="F1076">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:6">
+      <c r="A1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1077">
+        <v>1987</v>
+      </c>
+      <c r="C1077">
+        <v>0</v>
+      </c>
+      <c r="D1077">
+        <v>0</v>
+      </c>
+      <c r="E1077">
+        <v>0</v>
+      </c>
+      <c r="F1077">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:6">
+      <c r="A1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1078">
+        <v>1988</v>
+      </c>
+      <c r="C1078">
+        <v>0</v>
+      </c>
+      <c r="D1078">
+        <v>0</v>
+      </c>
+      <c r="E1078">
+        <v>0</v>
+      </c>
+      <c r="F1078">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:6">
+      <c r="A1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1079">
+        <v>1989</v>
+      </c>
+      <c r="C1079">
+        <v>0</v>
+      </c>
+      <c r="D1079">
+        <v>0</v>
+      </c>
+      <c r="E1079">
+        <v>0</v>
+      </c>
+      <c r="F1079">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:6">
+      <c r="A1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1080">
+        <v>1990</v>
+      </c>
+      <c r="C1080">
+        <v>0</v>
+      </c>
+      <c r="D1080">
+        <v>0</v>
+      </c>
+      <c r="E1080">
+        <v>0</v>
+      </c>
+      <c r="F1080">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:6">
+      <c r="A1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1081">
+        <v>1991</v>
+      </c>
+      <c r="C1081">
+        <v>0</v>
+      </c>
+      <c r="D1081">
+        <v>0</v>
+      </c>
+      <c r="E1081">
+        <v>0</v>
+      </c>
+      <c r="F1081">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:6">
+      <c r="A1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1082">
+        <v>1992</v>
+      </c>
+      <c r="C1082">
+        <v>0</v>
+      </c>
+      <c r="D1082">
+        <v>0</v>
+      </c>
+      <c r="E1082">
+        <v>0</v>
+      </c>
+      <c r="F1082">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:6">
+      <c r="A1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1083">
+        <v>1993</v>
+      </c>
+      <c r="C1083">
+        <v>0</v>
+      </c>
+      <c r="D1083">
+        <v>0</v>
+      </c>
+      <c r="E1083">
+        <v>0</v>
+      </c>
+      <c r="F1083">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:6">
+      <c r="A1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1084">
+        <v>1994</v>
+      </c>
+      <c r="C1084">
+        <v>0</v>
+      </c>
+      <c r="D1084">
+        <v>0</v>
+      </c>
+      <c r="E1084">
+        <v>0</v>
+      </c>
+      <c r="F1084">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:6">
+      <c r="A1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1085">
+        <v>1995</v>
+      </c>
+      <c r="C1085">
+        <v>0</v>
+      </c>
+      <c r="D1085">
+        <v>0</v>
+      </c>
+      <c r="E1085">
+        <v>0</v>
+      </c>
+      <c r="F1085">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:6">
+      <c r="A1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1086">
+        <v>1996</v>
+      </c>
+      <c r="C1086">
+        <v>0</v>
+      </c>
+      <c r="D1086">
+        <v>0</v>
+      </c>
+      <c r="E1086">
+        <v>0</v>
+      </c>
+      <c r="F1086">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:6">
+      <c r="A1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1087">
+        <v>1997</v>
+      </c>
+      <c r="C1087">
+        <v>0</v>
+      </c>
+      <c r="D1087">
+        <v>0</v>
+      </c>
+      <c r="E1087">
+        <v>0</v>
+      </c>
+      <c r="F1087">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:6">
+      <c r="A1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1088">
+        <v>1998</v>
+      </c>
+      <c r="C1088">
+        <v>0</v>
+      </c>
+      <c r="D1088">
+        <v>0</v>
+      </c>
+      <c r="E1088">
+        <v>0</v>
+      </c>
+      <c r="F1088">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:6">
+      <c r="A1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1089">
+        <v>1999</v>
+      </c>
+      <c r="C1089">
+        <v>0</v>
+      </c>
+      <c r="D1089">
+        <v>0</v>
+      </c>
+      <c r="E1089">
+        <v>0</v>
+      </c>
+      <c r="F1089">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:6">
+      <c r="A1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1090">
+        <v>2000</v>
+      </c>
+      <c r="C1090">
+        <v>0</v>
+      </c>
+      <c r="D1090">
+        <v>0</v>
+      </c>
+      <c r="E1090">
+        <v>0</v>
+      </c>
+      <c r="F1090">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:6">
+      <c r="A1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1091">
+        <v>2001</v>
+      </c>
+      <c r="C1091">
+        <v>0</v>
+      </c>
+      <c r="D1091">
+        <v>0</v>
+      </c>
+      <c r="E1091">
+        <v>0</v>
+      </c>
+      <c r="F1091">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:6">
+      <c r="A1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1092">
+        <v>2002</v>
+      </c>
+      <c r="C1092">
+        <v>0</v>
+      </c>
+      <c r="D1092">
+        <v>0</v>
+      </c>
+      <c r="E1092">
+        <v>0</v>
+      </c>
+      <c r="F1092">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:6">
+      <c r="A1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1093">
+        <v>2003</v>
+      </c>
+      <c r="C1093">
+        <v>0</v>
+      </c>
+      <c r="D1093">
+        <v>0</v>
+      </c>
+      <c r="E1093">
+        <v>0</v>
+      </c>
+      <c r="F1093">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:6">
+      <c r="A1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1094">
+        <v>2004</v>
+      </c>
+      <c r="C1094">
+        <v>0</v>
+      </c>
+      <c r="D1094">
+        <v>0</v>
+      </c>
+      <c r="E1094">
+        <v>0</v>
+      </c>
+      <c r="F1094">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:6">
+      <c r="A1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1095">
+        <v>2005</v>
+      </c>
+      <c r="C1095">
+        <v>0</v>
+      </c>
+      <c r="D1095">
+        <v>0</v>
+      </c>
+      <c r="E1095">
+        <v>0</v>
+      </c>
+      <c r="F1095">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:6">
+      <c r="A1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1096">
+        <v>2006</v>
+      </c>
+      <c r="C1096">
+        <v>0</v>
+      </c>
+      <c r="D1096">
+        <v>0</v>
+      </c>
+      <c r="E1096">
+        <v>0</v>
+      </c>
+      <c r="F1096">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:6">
+      <c r="A1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1097">
+        <v>2007</v>
+      </c>
+      <c r="C1097">
+        <v>0</v>
+      </c>
+      <c r="D1097">
+        <v>0</v>
+      </c>
+      <c r="E1097">
+        <v>0</v>
+      </c>
+      <c r="F1097">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:6">
+      <c r="A1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1098">
+        <v>2008</v>
+      </c>
+      <c r="C1098">
+        <v>0</v>
+      </c>
+      <c r="D1098">
+        <v>0</v>
+      </c>
+      <c r="E1098">
+        <v>0</v>
+      </c>
+      <c r="F1098">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:6">
+      <c r="A1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1099">
+        <v>2009</v>
+      </c>
+      <c r="C1099">
+        <v>0</v>
+      </c>
+      <c r="D1099">
+        <v>0</v>
+      </c>
+      <c r="E1099">
+        <v>0</v>
+      </c>
+      <c r="F1099">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:6">
+      <c r="A1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1100">
+        <v>2010</v>
+      </c>
+      <c r="C1100">
+        <v>0</v>
+      </c>
+      <c r="D1100">
+        <v>0</v>
+      </c>
+      <c r="E1100">
+        <v>0</v>
+      </c>
+      <c r="F1100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:6">
+      <c r="A1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1101">
+        <v>2011</v>
+      </c>
+      <c r="C1101">
+        <v>0</v>
+      </c>
+      <c r="D1101">
+        <v>0</v>
+      </c>
+      <c r="E1101">
+        <v>0</v>
+      </c>
+      <c r="F1101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:6">
+      <c r="A1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1102">
+        <v>2012</v>
+      </c>
+      <c r="C1102">
+        <v>0</v>
+      </c>
+      <c r="D1102">
+        <v>0</v>
+      </c>
+      <c r="E1102">
+        <v>0</v>
+      </c>
+      <c r="F1102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:6">
+      <c r="A1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1103">
+        <v>2013</v>
+      </c>
+      <c r="C1103">
+        <v>0</v>
+      </c>
+      <c r="D1103">
+        <v>0</v>
+      </c>
+      <c r="E1103">
+        <v>0</v>
+      </c>
+      <c r="F1103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:6">
+      <c r="A1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1104">
+        <v>2014</v>
+      </c>
+      <c r="C1104">
+        <v>0</v>
+      </c>
+      <c r="D1104">
+        <v>0</v>
+      </c>
+      <c r="E1104">
+        <v>0</v>
+      </c>
+      <c r="F1104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:6">
+      <c r="A1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1105">
+        <v>2015</v>
+      </c>
+      <c r="C1105">
+        <v>0</v>
+      </c>
+      <c r="D1105">
+        <v>0</v>
+      </c>
+      <c r="E1105">
+        <v>0</v>
+      </c>
+      <c r="F1105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:6">
+      <c r="A1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1106">
+        <v>2016</v>
+      </c>
+      <c r="C1106">
+        <v>0</v>
+      </c>
+      <c r="D1106">
+        <v>0</v>
+      </c>
+      <c r="E1106">
+        <v>0</v>
+      </c>
+      <c r="F1106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:6">
+      <c r="A1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1107">
+        <v>2017</v>
+      </c>
+      <c r="C1107">
+        <v>0</v>
+      </c>
+      <c r="D1107">
+        <v>0</v>
+      </c>
+      <c r="E1107">
+        <v>0</v>
+      </c>
+      <c r="F1107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:6">
+      <c r="A1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1108">
+        <v>2018</v>
+      </c>
+      <c r="C1108">
+        <v>0</v>
+      </c>
+      <c r="D1108">
+        <v>0</v>
+      </c>
+      <c r="E1108">
+        <v>0</v>
+      </c>
+      <c r="F1108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:6">
+      <c r="A1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1109">
+        <v>2019</v>
+      </c>
+      <c r="C1109">
+        <v>0</v>
+      </c>
+      <c r="D1109">
+        <v>0</v>
+      </c>
+      <c r="E1109">
+        <v>0</v>
+      </c>
+      <c r="F1109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:6">
+      <c r="A1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1110">
+        <v>2020</v>
+      </c>
+      <c r="C1110">
+        <v>0</v>
+      </c>
+      <c r="D1110">
+        <v>0</v>
+      </c>
+      <c r="E1110">
+        <v>0</v>
+      </c>
+      <c r="F1110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:6">
+      <c r="A1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1111">
+        <v>2021</v>
+      </c>
+      <c r="C1111">
+        <v>0</v>
+      </c>
+      <c r="D1111">
+        <v>0</v>
+      </c>
+      <c r="E1111">
+        <v>0</v>
+      </c>
+      <c r="F1111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:6">
+      <c r="A1112" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1112">
+        <v>2022</v>
+      </c>
+      <c r="C1112">
+        <v>0</v>
+      </c>
+      <c r="D1112">
+        <v>0</v>
+      </c>
+      <c r="E1112">
+        <v>0</v>
+      </c>
+      <c r="F1112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:6">
+      <c r="A1113" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1113">
+        <v>2023</v>
+      </c>
+      <c r="C1113">
+        <v>0</v>
+      </c>
+      <c r="D1113">
+        <v>0</v>
+      </c>
+      <c r="E1113">
+        <v>0</v>
+      </c>
+      <c r="F1113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:6">
+      <c r="A1114" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1114">
+        <v>2024</v>
+      </c>
+      <c r="C1114">
+        <v>0</v>
+      </c>
+      <c r="D1114">
+        <v>0</v>
+      </c>
+      <c r="E1114">
+        <v>0</v>
+      </c>
+      <c r="F1114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:6">
+      <c r="A1115" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1115">
+        <v>2025</v>
+      </c>
+      <c r="C1115">
+        <v>0</v>
+      </c>
+      <c r="D1115">
+        <v>0</v>
+      </c>
+      <c r="E1115">
+        <v>0</v>
+      </c>
+      <c r="F1115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:6">
+      <c r="A1116" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1116">
+        <v>2026</v>
+      </c>
+      <c r="C1116">
+        <v>0</v>
+      </c>
+      <c r="D1116">
+        <v>0</v>
+      </c>
+      <c r="E1116">
+        <v>0</v>
+      </c>
+      <c r="F1116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:6">
+      <c r="A1117" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1117">
+        <v>2027</v>
+      </c>
+      <c r="C1117">
+        <v>0</v>
+      </c>
+      <c r="D1117">
+        <v>0</v>
+      </c>
+      <c r="E1117">
+        <v>0</v>
+      </c>
+      <c r="F1117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:6">
+      <c r="A1118" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1118">
+        <v>2028</v>
+      </c>
+      <c r="C1118">
+        <v>0</v>
+      </c>
+      <c r="D1118">
+        <v>0</v>
+      </c>
+      <c r="E1118">
+        <v>0</v>
+      </c>
+      <c r="F1118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:6">
+      <c r="A1119" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1119">
+        <v>2029</v>
+      </c>
+      <c r="C1119">
+        <v>0</v>
+      </c>
+      <c r="D1119">
+        <v>0</v>
+      </c>
+      <c r="E1119">
+        <v>0</v>
+      </c>
+      <c r="F1119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:6">
+      <c r="A1120" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1120">
+        <v>2030</v>
+      </c>
+      <c r="C1120">
+        <v>0</v>
+      </c>
+      <c r="D1120">
+        <v>0</v>
+      </c>
+      <c r="E1120">
+        <v>0</v>
+      </c>
+      <c r="F1120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:6">
+      <c r="A1121" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1121">
+        <v>2031</v>
+      </c>
+      <c r="C1121">
+        <v>0</v>
+      </c>
+      <c r="D1121">
+        <v>0</v>
+      </c>
+      <c r="E1121">
+        <v>0</v>
+      </c>
+      <c r="F1121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:6">
+      <c r="A1122" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1122">
+        <v>2032</v>
+      </c>
+      <c r="C1122">
+        <v>0</v>
+      </c>
+      <c r="D1122">
+        <v>0</v>
+      </c>
+      <c r="E1122">
+        <v>0</v>
+      </c>
+      <c r="F1122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:6">
+      <c r="A1123" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1123">
+        <v>2033</v>
+      </c>
+      <c r="C1123">
+        <v>0</v>
+      </c>
+      <c r="D1123">
+        <v>0</v>
+      </c>
+      <c r="E1123">
+        <v>0</v>
+      </c>
+      <c r="F1123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:6">
+      <c r="A1124" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1124">
+        <v>2034</v>
+      </c>
+      <c r="C1124">
+        <v>0</v>
+      </c>
+      <c r="D1124">
+        <v>0</v>
+      </c>
+      <c r="E1124">
+        <v>0</v>
+      </c>
+      <c r="F1124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:6">
+      <c r="A1125" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1125">
+        <v>2035</v>
+      </c>
+      <c r="C1125">
+        <v>0</v>
+      </c>
+      <c r="D1125">
+        <v>0</v>
+      </c>
+      <c r="E1125">
+        <v>0</v>
+      </c>
+      <c r="F1125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:6">
+      <c r="A1126" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1126">
+        <v>2036</v>
+      </c>
+      <c r="C1126">
+        <v>0</v>
+      </c>
+      <c r="D1126">
+        <v>0</v>
+      </c>
+      <c r="E1126">
+        <v>0</v>
+      </c>
+      <c r="F1126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:6">
+      <c r="A1127" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1127">
+        <v>2037</v>
+      </c>
+      <c r="C1127">
+        <v>0</v>
+      </c>
+      <c r="D1127">
+        <v>0</v>
+      </c>
+      <c r="E1127">
+        <v>0</v>
+      </c>
+      <c r="F1127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:6">
+      <c r="A1128" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1128">
+        <v>2038</v>
+      </c>
+      <c r="C1128">
+        <v>0</v>
+      </c>
+      <c r="D1128">
+        <v>0</v>
+      </c>
+      <c r="E1128">
+        <v>0</v>
+      </c>
+      <c r="F1128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:6">
+      <c r="A1129" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1129">
+        <v>2039</v>
+      </c>
+      <c r="C1129">
+        <v>0</v>
+      </c>
+      <c r="D1129">
+        <v>0</v>
+      </c>
+      <c r="E1129">
+        <v>0</v>
+      </c>
+      <c r="F1129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:6">
+      <c r="A1130" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1130">
+        <v>2040</v>
+      </c>
+      <c r="C1130">
+        <v>0</v>
+      </c>
+      <c r="D1130">
+        <v>0</v>
+      </c>
+      <c r="E1130">
+        <v>0</v>
+      </c>
+      <c r="F1130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:6">
+      <c r="A1131" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1131">
+        <v>2041</v>
+      </c>
+      <c r="C1131">
+        <v>0</v>
+      </c>
+      <c r="D1131">
+        <v>0</v>
+      </c>
+      <c r="E1131">
+        <v>0</v>
+      </c>
+      <c r="F1131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:6">
+      <c r="A1132" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1132">
+        <v>2042</v>
+      </c>
+      <c r="C1132">
+        <v>0</v>
+      </c>
+      <c r="D1132">
+        <v>0</v>
+      </c>
+      <c r="E1132">
+        <v>0</v>
+      </c>
+      <c r="F1132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:6">
+      <c r="A1133" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1133">
+        <v>2043</v>
+      </c>
+      <c r="C1133">
+        <v>0</v>
+      </c>
+      <c r="D1133">
+        <v>0</v>
+      </c>
+      <c r="E1133">
+        <v>0</v>
+      </c>
+      <c r="F1133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:6">
+      <c r="A1134" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1134">
+        <v>2044</v>
+      </c>
+      <c r="C1134">
+        <v>0</v>
+      </c>
+      <c r="D1134">
+        <v>0</v>
+      </c>
+      <c r="E1134">
+        <v>0</v>
+      </c>
+      <c r="F1134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:6">
+      <c r="A1135" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1135">
+        <v>2045</v>
+      </c>
+      <c r="C1135">
+        <v>0</v>
+      </c>
+      <c r="D1135">
+        <v>0</v>
+      </c>
+      <c r="E1135">
+        <v>0</v>
+      </c>
+      <c r="F1135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:6">
+      <c r="A1136" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1136">
+        <v>1920</v>
+      </c>
+      <c r="C1136">
+        <v>0</v>
+      </c>
+      <c r="D1136">
+        <v>0</v>
+      </c>
+      <c r="E1136">
+        <v>0</v>
+      </c>
+      <c r="F1136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:6">
+      <c r="A1137" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1137">
+        <v>1921</v>
+      </c>
+      <c r="C1137">
+        <v>0</v>
+      </c>
+      <c r="D1137">
+        <v>0</v>
+      </c>
+      <c r="E1137">
+        <v>0</v>
+      </c>
+      <c r="F1137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:6">
+      <c r="A1138" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1138">
+        <v>1922</v>
+      </c>
+      <c r="C1138">
+        <v>0</v>
+      </c>
+      <c r="D1138">
+        <v>0</v>
+      </c>
+      <c r="E1138">
+        <v>0</v>
+      </c>
+      <c r="F1138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:6">
+      <c r="A1139" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1139">
+        <v>1923</v>
+      </c>
+      <c r="C1139">
+        <v>0</v>
+      </c>
+      <c r="D1139">
+        <v>0</v>
+      </c>
+      <c r="E1139">
+        <v>0</v>
+      </c>
+      <c r="F1139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:6">
+      <c r="A1140" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1140">
+        <v>1924</v>
+      </c>
+      <c r="C1140">
+        <v>0</v>
+      </c>
+      <c r="D1140">
+        <v>0</v>
+      </c>
+      <c r="E1140">
+        <v>0</v>
+      </c>
+      <c r="F1140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:6">
+      <c r="A1141" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1141">
+        <v>1925</v>
+      </c>
+      <c r="C1141">
+        <v>0</v>
+      </c>
+      <c r="D1141">
+        <v>0</v>
+      </c>
+      <c r="E1141">
+        <v>0</v>
+      </c>
+      <c r="F1141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:6">
+      <c r="A1142" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1142">
+        <v>1926</v>
+      </c>
+      <c r="C1142">
+        <v>0</v>
+      </c>
+      <c r="D1142">
+        <v>0</v>
+      </c>
+      <c r="E1142">
+        <v>0</v>
+      </c>
+      <c r="F1142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:6">
+      <c r="A1143" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1143">
+        <v>1927</v>
+      </c>
+      <c r="C1143">
+        <v>0</v>
+      </c>
+      <c r="D1143">
+        <v>0</v>
+      </c>
+      <c r="E1143">
+        <v>0</v>
+      </c>
+      <c r="F1143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:6">
+      <c r="A1144" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1144">
+        <v>1928</v>
+      </c>
+      <c r="C1144">
+        <v>0</v>
+      </c>
+      <c r="D1144">
+        <v>0</v>
+      </c>
+      <c r="E1144">
+        <v>0</v>
+      </c>
+      <c r="F1144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:6">
+      <c r="A1145" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1145">
+        <v>1929</v>
+      </c>
+      <c r="C1145">
+        <v>0</v>
+      </c>
+      <c r="D1145">
+        <v>0</v>
+      </c>
+      <c r="E1145">
+        <v>0</v>
+      </c>
+      <c r="F1145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:6">
+      <c r="A1146" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1146">
+        <v>1930</v>
+      </c>
+      <c r="C1146">
+        <v>0</v>
+      </c>
+      <c r="D1146">
+        <v>0</v>
+      </c>
+      <c r="E1146">
+        <v>0</v>
+      </c>
+      <c r="F1146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:6">
+      <c r="A1147" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1147">
+        <v>1931</v>
+      </c>
+      <c r="C1147">
+        <v>0</v>
+      </c>
+      <c r="D1147">
+        <v>0</v>
+      </c>
+      <c r="E1147">
+        <v>0</v>
+      </c>
+      <c r="F1147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:6">
+      <c r="A1148" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1148">
+        <v>1932</v>
+      </c>
+      <c r="C1148">
+        <v>0</v>
+      </c>
+      <c r="D1148">
+        <v>0</v>
+      </c>
+      <c r="E1148">
+        <v>0</v>
+      </c>
+      <c r="F1148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:6">
+      <c r="A1149" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1149">
+        <v>1933</v>
+      </c>
+      <c r="C1149">
+        <v>0</v>
+      </c>
+      <c r="D1149">
+        <v>0</v>
+      </c>
+      <c r="E1149">
+        <v>0</v>
+      </c>
+      <c r="F1149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:6">
+      <c r="A1150" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1150">
+        <v>1934</v>
+      </c>
+      <c r="C1150">
+        <v>0</v>
+      </c>
+      <c r="D1150">
+        <v>0</v>
+      </c>
+      <c r="E1150">
+        <v>0</v>
+      </c>
+      <c r="F1150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:6">
+      <c r="A1151" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1151">
+        <v>1935</v>
+      </c>
+      <c r="C1151">
+        <v>0</v>
+      </c>
+      <c r="D1151">
+        <v>0</v>
+      </c>
+      <c r="E1151">
+        <v>0</v>
+      </c>
+      <c r="F1151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:6">
+      <c r="A1152" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1152">
+        <v>1936</v>
+      </c>
+      <c r="C1152">
+        <v>0</v>
+      </c>
+      <c r="D1152">
+        <v>0</v>
+      </c>
+      <c r="E1152">
+        <v>0</v>
+      </c>
+      <c r="F1152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:6">
+      <c r="A1153" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1153">
+        <v>1937</v>
+      </c>
+      <c r="C1153">
+        <v>0</v>
+      </c>
+      <c r="D1153">
+        <v>0</v>
+      </c>
+      <c r="E1153">
+        <v>0</v>
+      </c>
+      <c r="F1153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:6">
+      <c r="A1154" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1154">
+        <v>1938</v>
+      </c>
+      <c r="C1154">
+        <v>0</v>
+      </c>
+      <c r="D1154">
+        <v>0</v>
+      </c>
+      <c r="E1154">
+        <v>0</v>
+      </c>
+      <c r="F1154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:6">
+      <c r="A1155" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1155">
+        <v>1939</v>
+      </c>
+      <c r="C1155">
+        <v>0</v>
+      </c>
+      <c r="D1155">
+        <v>0</v>
+      </c>
+      <c r="E1155">
+        <v>0</v>
+      </c>
+      <c r="F1155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:6">
+      <c r="A1156" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1156">
+        <v>1940</v>
+      </c>
+      <c r="C1156">
+        <v>0</v>
+      </c>
+      <c r="D1156">
+        <v>0</v>
+      </c>
+      <c r="E1156">
+        <v>0</v>
+      </c>
+      <c r="F1156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:6">
+      <c r="A1157" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1157">
+        <v>1941</v>
+      </c>
+      <c r="C1157">
+        <v>0</v>
+      </c>
+      <c r="D1157">
+        <v>0</v>
+      </c>
+      <c r="E1157">
+        <v>0</v>
+      </c>
+      <c r="F1157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:6">
+      <c r="A1158" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1158">
+        <v>1942</v>
+      </c>
+      <c r="C1158">
+        <v>0</v>
+      </c>
+      <c r="D1158">
+        <v>0</v>
+      </c>
+      <c r="E1158">
+        <v>0</v>
+      </c>
+      <c r="F1158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:6">
+      <c r="A1159" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1159">
+        <v>1943</v>
+      </c>
+      <c r="C1159">
+        <v>0</v>
+      </c>
+      <c r="D1159">
+        <v>0</v>
+      </c>
+      <c r="E1159">
+        <v>0</v>
+      </c>
+      <c r="F1159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:6">
+      <c r="A1160" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1160">
+        <v>1944</v>
+      </c>
+      <c r="C1160">
+        <v>0</v>
+      </c>
+      <c r="D1160">
+        <v>0</v>
+      </c>
+      <c r="E1160">
+        <v>0</v>
+      </c>
+      <c r="F1160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:6">
+      <c r="A1161" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1161">
+        <v>1945</v>
+      </c>
+      <c r="C1161">
+        <v>0</v>
+      </c>
+      <c r="D1161">
+        <v>0</v>
+      </c>
+      <c r="E1161">
+        <v>0</v>
+      </c>
+      <c r="F1161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:6">
+      <c r="A1162" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1162">
+        <v>1946</v>
+      </c>
+      <c r="C1162">
+        <v>0</v>
+      </c>
+      <c r="D1162">
+        <v>0</v>
+      </c>
+      <c r="E1162">
+        <v>0</v>
+      </c>
+      <c r="F1162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:6">
+      <c r="A1163" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1163">
+        <v>1947</v>
+      </c>
+      <c r="C1163">
+        <v>0</v>
+      </c>
+      <c r="D1163">
+        <v>0</v>
+      </c>
+      <c r="E1163">
+        <v>0</v>
+      </c>
+      <c r="F1163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:6">
+      <c r="A1164" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1164">
+        <v>1948</v>
+      </c>
+      <c r="C1164">
+        <v>0</v>
+      </c>
+      <c r="D1164">
+        <v>0</v>
+      </c>
+      <c r="E1164">
+        <v>0</v>
+      </c>
+      <c r="F1164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:6">
+      <c r="A1165" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1165">
+        <v>1949</v>
+      </c>
+      <c r="C1165">
+        <v>0</v>
+      </c>
+      <c r="D1165">
+        <v>0</v>
+      </c>
+      <c r="E1165">
+        <v>0</v>
+      </c>
+      <c r="F1165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:6">
+      <c r="A1166" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1166">
+        <v>1950</v>
+      </c>
+      <c r="C1166">
+        <v>0</v>
+      </c>
+      <c r="D1166">
+        <v>0</v>
+      </c>
+      <c r="E1166">
+        <v>0</v>
+      </c>
+      <c r="F1166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:6">
+      <c r="A1167" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1167">
+        <v>1951</v>
+      </c>
+      <c r="C1167">
+        <v>0</v>
+      </c>
+      <c r="D1167">
+        <v>0</v>
+      </c>
+      <c r="E1167">
+        <v>0</v>
+      </c>
+      <c r="F1167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:6">
+      <c r="A1168" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1168">
+        <v>1952</v>
+      </c>
+      <c r="C1168">
+        <v>0</v>
+      </c>
+      <c r="D1168">
+        <v>0</v>
+      </c>
+      <c r="E1168">
+        <v>0</v>
+      </c>
+      <c r="F1168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:6">
+      <c r="A1169" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1169">
+        <v>1953</v>
+      </c>
+      <c r="C1169">
+        <v>0</v>
+      </c>
+      <c r="D1169">
+        <v>0</v>
+      </c>
+      <c r="E1169">
+        <v>0</v>
+      </c>
+      <c r="F1169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:6">
+      <c r="A1170" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1170">
+        <v>1954</v>
+      </c>
+      <c r="C1170">
+        <v>0</v>
+      </c>
+      <c r="D1170">
+        <v>0</v>
+      </c>
+      <c r="E1170">
+        <v>0</v>
+      </c>
+      <c r="F1170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:6">
+      <c r="A1171" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1171">
+        <v>1955</v>
+      </c>
+      <c r="C1171">
+        <v>0</v>
+      </c>
+      <c r="D1171">
+        <v>0</v>
+      </c>
+      <c r="E1171">
+        <v>0</v>
+      </c>
+      <c r="F1171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:6">
+      <c r="A1172" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1172">
+        <v>1956</v>
+      </c>
+      <c r="C1172">
+        <v>0</v>
+      </c>
+      <c r="D1172">
+        <v>0</v>
+      </c>
+      <c r="E1172">
+        <v>0</v>
+      </c>
+      <c r="F1172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:6">
+      <c r="A1173" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1173">
+        <v>1957</v>
+      </c>
+      <c r="C1173">
+        <v>0</v>
+      </c>
+      <c r="D1173">
+        <v>0</v>
+      </c>
+      <c r="E1173">
+        <v>0</v>
+      </c>
+      <c r="F1173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:6">
+      <c r="A1174" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1174">
+        <v>1958</v>
+      </c>
+      <c r="C1174">
+        <v>0</v>
+      </c>
+      <c r="D1174">
+        <v>0</v>
+      </c>
+      <c r="E1174">
+        <v>0</v>
+      </c>
+      <c r="F1174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:6">
+      <c r="A1175" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1175">
+        <v>1959</v>
+      </c>
+      <c r="C1175">
+        <v>0</v>
+      </c>
+      <c r="D1175">
+        <v>0</v>
+      </c>
+      <c r="E1175">
+        <v>0</v>
+      </c>
+      <c r="F1175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:6">
+      <c r="A1176" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1176">
+        <v>1960</v>
+      </c>
+      <c r="C1176">
+        <v>0</v>
+      </c>
+      <c r="D1176">
+        <v>0</v>
+      </c>
+      <c r="E1176">
+        <v>0</v>
+      </c>
+      <c r="F1176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:6">
+      <c r="A1177" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1177">
+        <v>1961</v>
+      </c>
+      <c r="C1177">
+        <v>0</v>
+      </c>
+      <c r="D1177">
+        <v>0</v>
+      </c>
+      <c r="E1177">
+        <v>0</v>
+      </c>
+      <c r="F1177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:6">
+      <c r="A1178" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1178">
+        <v>1962</v>
+      </c>
+      <c r="C1178">
+        <v>0</v>
+      </c>
+      <c r="D1178">
+        <v>0</v>
+      </c>
+      <c r="E1178">
+        <v>0</v>
+      </c>
+      <c r="F1178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:6">
+      <c r="A1179" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1179">
+        <v>1963</v>
+      </c>
+      <c r="C1179">
+        <v>0</v>
+      </c>
+      <c r="D1179">
+        <v>0</v>
+      </c>
+      <c r="E1179">
+        <v>0</v>
+      </c>
+      <c r="F1179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:6">
+      <c r="A1180" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1180">
+        <v>1964</v>
+      </c>
+      <c r="C1180">
+        <v>0</v>
+      </c>
+      <c r="D1180">
+        <v>0</v>
+      </c>
+      <c r="E1180">
+        <v>0</v>
+      </c>
+      <c r="F1180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:6">
+      <c r="A1181" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1181">
+        <v>1965</v>
+      </c>
+      <c r="C1181">
+        <v>0</v>
+      </c>
+      <c r="D1181">
+        <v>0</v>
+      </c>
+      <c r="E1181">
+        <v>0</v>
+      </c>
+      <c r="F1181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:6">
+      <c r="A1182" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1182">
+        <v>1966</v>
+      </c>
+      <c r="C1182">
+        <v>0</v>
+      </c>
+      <c r="D1182">
+        <v>0</v>
+      </c>
+      <c r="E1182">
+        <v>0</v>
+      </c>
+      <c r="F1182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:6">
+      <c r="A1183" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1183">
+        <v>1967</v>
+      </c>
+      <c r="C1183">
+        <v>0</v>
+      </c>
+      <c r="D1183">
+        <v>0</v>
+      </c>
+      <c r="E1183">
+        <v>0</v>
+      </c>
+      <c r="F1183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:6">
+      <c r="A1184" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1184">
+        <v>1968</v>
+      </c>
+      <c r="C1184">
+        <v>0</v>
+      </c>
+      <c r="D1184">
+        <v>0</v>
+      </c>
+      <c r="E1184">
+        <v>0</v>
+      </c>
+      <c r="F1184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:6">
+      <c r="A1185" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1185">
+        <v>1969</v>
+      </c>
+      <c r="C1185">
+        <v>0</v>
+      </c>
+      <c r="D1185">
+        <v>0</v>
+      </c>
+      <c r="E1185">
+        <v>0</v>
+      </c>
+      <c r="F1185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:6">
+      <c r="A1186" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1186">
+        <v>1970</v>
+      </c>
+      <c r="C1186">
+        <v>0</v>
+      </c>
+      <c r="D1186">
+        <v>0</v>
+      </c>
+      <c r="E1186">
+        <v>0</v>
+      </c>
+      <c r="F1186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:6">
+      <c r="A1187" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1187">
+        <v>1971</v>
+      </c>
+      <c r="C1187">
+        <v>0</v>
+      </c>
+      <c r="D1187">
+        <v>0</v>
+      </c>
+      <c r="E1187">
+        <v>0</v>
+      </c>
+      <c r="F1187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:6">
+      <c r="A1188" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1188">
+        <v>1972</v>
+      </c>
+      <c r="C1188">
+        <v>0</v>
+      </c>
+      <c r="D1188">
+        <v>0</v>
+      </c>
+      <c r="E1188">
+        <v>0</v>
+      </c>
+      <c r="F1188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:6">
+      <c r="A1189" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1189">
+        <v>1973</v>
+      </c>
+      <c r="C1189">
+        <v>0</v>
+      </c>
+      <c r="D1189">
+        <v>0</v>
+      </c>
+      <c r="E1189">
+        <v>0</v>
+      </c>
+      <c r="F1189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:6">
+      <c r="A1190" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1190">
+        <v>1974</v>
+      </c>
+      <c r="C1190">
+        <v>0</v>
+      </c>
+      <c r="D1190">
+        <v>0</v>
+      </c>
+      <c r="E1190">
+        <v>0</v>
+      </c>
+      <c r="F1190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:6">
+      <c r="A1191" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1191">
+        <v>1975</v>
+      </c>
+      <c r="C1191">
+        <v>0</v>
+      </c>
+      <c r="D1191">
+        <v>0</v>
+      </c>
+      <c r="E1191">
+        <v>0</v>
+      </c>
+      <c r="F1191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:6">
+      <c r="A1192" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1192">
+        <v>1976</v>
+      </c>
+      <c r="C1192">
+        <v>0</v>
+      </c>
+      <c r="D1192">
+        <v>0</v>
+      </c>
+      <c r="E1192">
+        <v>0</v>
+      </c>
+      <c r="F1192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:6">
+      <c r="A1193" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1193">
+        <v>1977</v>
+      </c>
+      <c r="C1193">
+        <v>0</v>
+      </c>
+      <c r="D1193">
+        <v>0</v>
+      </c>
+      <c r="E1193">
+        <v>0</v>
+      </c>
+      <c r="F1193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:6">
+      <c r="A1194" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1194">
+        <v>1978</v>
+      </c>
+      <c r="C1194">
+        <v>0</v>
+      </c>
+      <c r="D1194">
+        <v>0</v>
+      </c>
+      <c r="E1194">
+        <v>0</v>
+      </c>
+      <c r="F1194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:6">
+      <c r="A1195" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1195">
+        <v>1979</v>
+      </c>
+      <c r="C1195">
+        <v>0</v>
+      </c>
+      <c r="D1195">
+        <v>0</v>
+      </c>
+      <c r="E1195">
+        <v>0</v>
+      </c>
+      <c r="F1195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:6">
+      <c r="A1196" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1196">
+        <v>1980</v>
+      </c>
+      <c r="C1196">
+        <v>0</v>
+      </c>
+      <c r="D1196">
+        <v>0</v>
+      </c>
+      <c r="E1196">
+        <v>0</v>
+      </c>
+      <c r="F1196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:6">
+      <c r="A1197" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1197">
+        <v>1981</v>
+      </c>
+      <c r="C1197">
+        <v>0</v>
+      </c>
+      <c r="D1197">
+        <v>0</v>
+      </c>
+      <c r="E1197">
+        <v>0</v>
+      </c>
+      <c r="F1197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:6">
+      <c r="A1198" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1198">
+        <v>1982</v>
+      </c>
+      <c r="C1198">
+        <v>0</v>
+      </c>
+      <c r="D1198">
+        <v>0</v>
+      </c>
+      <c r="E1198">
+        <v>0</v>
+      </c>
+      <c r="F1198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:6">
+      <c r="A1199" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1199">
+        <v>1983</v>
+      </c>
+      <c r="C1199">
+        <v>0</v>
+      </c>
+      <c r="D1199">
+        <v>0</v>
+      </c>
+      <c r="E1199">
+        <v>0</v>
+      </c>
+      <c r="F1199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:6">
+      <c r="A1200" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1200">
+        <v>1984</v>
+      </c>
+      <c r="C1200">
+        <v>0</v>
+      </c>
+      <c r="D1200">
+        <v>0</v>
+      </c>
+      <c r="E1200">
+        <v>0</v>
+      </c>
+      <c r="F1200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:6">
+      <c r="A1201" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1201">
+        <v>1985</v>
+      </c>
+      <c r="C1201">
+        <v>0</v>
+      </c>
+      <c r="D1201">
+        <v>0</v>
+      </c>
+      <c r="E1201">
+        <v>0</v>
+      </c>
+      <c r="F1201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:6">
+      <c r="A1202" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1202">
+        <v>1986</v>
+      </c>
+      <c r="C1202">
+        <v>0</v>
+      </c>
+      <c r="D1202">
+        <v>0</v>
+      </c>
+      <c r="E1202">
+        <v>0</v>
+      </c>
+      <c r="F1202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:6">
+      <c r="A1203" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1203">
+        <v>1987</v>
+      </c>
+      <c r="C1203">
+        <v>0</v>
+      </c>
+      <c r="D1203">
+        <v>0</v>
+      </c>
+      <c r="E1203">
+        <v>0</v>
+      </c>
+      <c r="F1203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:6">
+      <c r="A1204" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1204">
+        <v>1988</v>
+      </c>
+      <c r="C1204">
+        <v>0</v>
+      </c>
+      <c r="D1204">
+        <v>0</v>
+      </c>
+      <c r="E1204">
+        <v>0</v>
+      </c>
+      <c r="F1204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:6">
+      <c r="A1205" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1205">
+        <v>1989</v>
+      </c>
+      <c r="C1205">
+        <v>0</v>
+      </c>
+      <c r="D1205">
+        <v>0</v>
+      </c>
+      <c r="E1205">
+        <v>0</v>
+      </c>
+      <c r="F1205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:6">
+      <c r="A1206" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1206">
+        <v>1990</v>
+      </c>
+      <c r="C1206">
+        <v>0</v>
+      </c>
+      <c r="D1206">
+        <v>0</v>
+      </c>
+      <c r="E1206">
+        <v>0</v>
+      </c>
+      <c r="F1206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:6">
+      <c r="A1207" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1207">
+        <v>1991</v>
+      </c>
+      <c r="C1207">
+        <v>0</v>
+      </c>
+      <c r="D1207">
+        <v>0</v>
+      </c>
+      <c r="E1207">
+        <v>0</v>
+      </c>
+      <c r="F1207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:6">
+      <c r="A1208" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1208">
+        <v>1992</v>
+      </c>
+      <c r="C1208">
+        <v>0</v>
+      </c>
+      <c r="D1208">
+        <v>0</v>
+      </c>
+      <c r="E1208">
+        <v>0</v>
+      </c>
+      <c r="F1208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:6">
+      <c r="A1209" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1209">
+        <v>1993</v>
+      </c>
+      <c r="C1209">
+        <v>0</v>
+      </c>
+      <c r="D1209">
+        <v>0</v>
+      </c>
+      <c r="E1209">
+        <v>0</v>
+      </c>
+      <c r="F1209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:6">
+      <c r="A1210" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1210">
+        <v>1994</v>
+      </c>
+      <c r="C1210">
+        <v>0</v>
+      </c>
+      <c r="D1210">
+        <v>0</v>
+      </c>
+      <c r="E1210">
+        <v>0</v>
+      </c>
+      <c r="F1210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:6">
+      <c r="A1211" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1211">
+        <v>1995</v>
+      </c>
+      <c r="C1211">
+        <v>0</v>
+      </c>
+      <c r="D1211">
+        <v>0</v>
+      </c>
+      <c r="E1211">
+        <v>0</v>
+      </c>
+      <c r="F1211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:6">
+      <c r="A1212" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1212">
+        <v>1996</v>
+      </c>
+      <c r="C1212">
+        <v>0</v>
+      </c>
+      <c r="D1212">
+        <v>0</v>
+      </c>
+      <c r="E1212">
+        <v>0</v>
+      </c>
+      <c r="F1212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:6">
+      <c r="A1213" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1213">
+        <v>1997</v>
+      </c>
+      <c r="C1213">
+        <v>0</v>
+      </c>
+      <c r="D1213">
+        <v>0</v>
+      </c>
+      <c r="E1213">
+        <v>0</v>
+      </c>
+      <c r="F1213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:6">
+      <c r="A1214" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1214">
+        <v>1998</v>
+      </c>
+      <c r="C1214">
+        <v>0</v>
+      </c>
+      <c r="D1214">
+        <v>0</v>
+      </c>
+      <c r="E1214">
+        <v>0</v>
+      </c>
+      <c r="F1214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:6">
+      <c r="A1215" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1215">
+        <v>1999</v>
+      </c>
+      <c r="C1215">
+        <v>0</v>
+      </c>
+      <c r="D1215">
+        <v>0</v>
+      </c>
+      <c r="E1215">
+        <v>0</v>
+      </c>
+      <c r="F1215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:6">
+      <c r="A1216" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1216">
+        <v>2000</v>
+      </c>
+      <c r="C1216">
+        <v>0</v>
+      </c>
+      <c r="D1216">
+        <v>0</v>
+      </c>
+      <c r="E1216">
+        <v>0</v>
+      </c>
+      <c r="F1216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:6">
+      <c r="A1217" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1217">
+        <v>2001</v>
+      </c>
+      <c r="C1217">
+        <v>0</v>
+      </c>
+      <c r="D1217">
+        <v>0</v>
+      </c>
+      <c r="E1217">
+        <v>0</v>
+      </c>
+      <c r="F1217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:6">
+      <c r="A1218" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1218">
+        <v>2002</v>
+      </c>
+      <c r="C1218">
+        <v>0</v>
+      </c>
+      <c r="D1218">
+        <v>0</v>
+      </c>
+      <c r="E1218">
+        <v>0</v>
+      </c>
+      <c r="F1218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:6">
+      <c r="A1219" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1219">
+        <v>2003</v>
+      </c>
+      <c r="C1219">
+        <v>0</v>
+      </c>
+      <c r="D1219">
+        <v>0</v>
+      </c>
+      <c r="E1219">
+        <v>0</v>
+      </c>
+      <c r="F1219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:6">
+      <c r="A1220" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1220">
+        <v>2004</v>
+      </c>
+      <c r="C1220">
+        <v>0</v>
+      </c>
+      <c r="D1220">
+        <v>0</v>
+      </c>
+      <c r="E1220">
+        <v>0</v>
+      </c>
+      <c r="F1220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:6">
+      <c r="A1221" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1221">
+        <v>2005</v>
+      </c>
+      <c r="C1221">
+        <v>0</v>
+      </c>
+      <c r="D1221">
+        <v>0</v>
+      </c>
+      <c r="E1221">
+        <v>0</v>
+      </c>
+      <c r="F1221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:6">
+      <c r="A1222" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1222">
+        <v>2006</v>
+      </c>
+      <c r="C1222">
+        <v>0</v>
+      </c>
+      <c r="D1222">
+        <v>0</v>
+      </c>
+      <c r="E1222">
+        <v>0</v>
+      </c>
+      <c r="F1222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:6">
+      <c r="A1223" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1223">
+        <v>2007</v>
+      </c>
+      <c r="C1223">
+        <v>0</v>
+      </c>
+      <c r="D1223">
+        <v>0</v>
+      </c>
+      <c r="E1223">
+        <v>0</v>
+      </c>
+      <c r="F1223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:6">
+      <c r="A1224" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1224">
+        <v>2008</v>
+      </c>
+      <c r="C1224">
+        <v>0</v>
+      </c>
+      <c r="D1224">
+        <v>0</v>
+      </c>
+      <c r="E1224">
+        <v>0</v>
+      </c>
+      <c r="F1224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:6">
+      <c r="A1225" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1225">
+        <v>2009</v>
+      </c>
+      <c r="C1225">
+        <v>0</v>
+      </c>
+      <c r="D1225">
+        <v>0</v>
+      </c>
+      <c r="E1225">
+        <v>0</v>
+      </c>
+      <c r="F1225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:6">
+      <c r="A1226" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1226">
+        <v>2010</v>
+      </c>
+      <c r="C1226">
+        <v>0</v>
+      </c>
+      <c r="D1226">
+        <v>0</v>
+      </c>
+      <c r="E1226">
+        <v>0</v>
+      </c>
+      <c r="F1226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:6">
+      <c r="A1227" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1227">
+        <v>2011</v>
+      </c>
+      <c r="C1227">
+        <v>0</v>
+      </c>
+      <c r="D1227">
+        <v>0</v>
+      </c>
+      <c r="E1227">
+        <v>0</v>
+      </c>
+      <c r="F1227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:6">
+      <c r="A1228" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1228">
+        <v>2012</v>
+      </c>
+      <c r="C1228">
+        <v>0</v>
+      </c>
+      <c r="D1228">
+        <v>0</v>
+      </c>
+      <c r="E1228">
+        <v>0</v>
+      </c>
+      <c r="F1228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:6">
+      <c r="A1229" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1229">
+        <v>2013</v>
+      </c>
+      <c r="C1229">
+        <v>0</v>
+      </c>
+      <c r="D1229">
+        <v>0</v>
+      </c>
+      <c r="E1229">
+        <v>0</v>
+      </c>
+      <c r="F1229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:6">
+      <c r="A1230" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1230">
+        <v>2014</v>
+      </c>
+      <c r="C1230">
+        <v>0</v>
+      </c>
+      <c r="D1230">
+        <v>0</v>
+      </c>
+      <c r="E1230">
+        <v>0</v>
+      </c>
+      <c r="F1230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:6">
+      <c r="A1231" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1231">
+        <v>2015</v>
+      </c>
+      <c r="C1231">
+        <v>0</v>
+      </c>
+      <c r="D1231">
+        <v>0</v>
+      </c>
+      <c r="E1231">
+        <v>0</v>
+      </c>
+      <c r="F1231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:6">
+      <c r="A1232" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1232">
+        <v>2016</v>
+      </c>
+      <c r="C1232">
+        <v>0</v>
+      </c>
+      <c r="D1232">
+        <v>0</v>
+      </c>
+      <c r="E1232">
+        <v>0</v>
+      </c>
+      <c r="F1232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:6">
+      <c r="A1233" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1233">
+        <v>2017</v>
+      </c>
+      <c r="C1233">
+        <v>0</v>
+      </c>
+      <c r="D1233">
+        <v>0</v>
+      </c>
+      <c r="E1233">
+        <v>0</v>
+      </c>
+      <c r="F1233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:6">
+      <c r="A1234" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1234">
+        <v>2018</v>
+      </c>
+      <c r="C1234">
+        <v>0</v>
+      </c>
+      <c r="D1234">
+        <v>0</v>
+      </c>
+      <c r="E1234">
+        <v>0</v>
+      </c>
+      <c r="F1234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:6">
+      <c r="A1235" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1235">
+        <v>2019</v>
+      </c>
+      <c r="C1235">
+        <v>0</v>
+      </c>
+      <c r="D1235">
+        <v>0</v>
+      </c>
+      <c r="E1235">
+        <v>0</v>
+      </c>
+      <c r="F1235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:6">
+      <c r="A1236" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1236">
+        <v>2020</v>
+      </c>
+      <c r="C1236">
+        <v>0</v>
+      </c>
+      <c r="D1236">
+        <v>0</v>
+      </c>
+      <c r="E1236">
+        <v>0</v>
+      </c>
+      <c r="F1236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:6">
+      <c r="A1237" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1237">
+        <v>2021</v>
+      </c>
+      <c r="C1237">
+        <v>0</v>
+      </c>
+      <c r="D1237">
+        <v>0</v>
+      </c>
+      <c r="E1237">
+        <v>0</v>
+      </c>
+      <c r="F1237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:6">
+      <c r="A1238" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1238">
+        <v>2022</v>
+      </c>
+      <c r="C1238">
+        <v>0</v>
+      </c>
+      <c r="D1238">
+        <v>0</v>
+      </c>
+      <c r="E1238">
+        <v>0</v>
+      </c>
+      <c r="F1238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:6">
+      <c r="A1239" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1239">
+        <v>2023</v>
+      </c>
+      <c r="C1239">
+        <v>0</v>
+      </c>
+      <c r="D1239">
+        <v>0</v>
+      </c>
+      <c r="E1239">
+        <v>0</v>
+      </c>
+      <c r="F1239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:6">
+      <c r="A1240" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1240">
+        <v>2024</v>
+      </c>
+      <c r="C1240">
+        <v>0</v>
+      </c>
+      <c r="D1240">
+        <v>0</v>
+      </c>
+      <c r="E1240">
+        <v>0</v>
+      </c>
+      <c r="F1240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:6">
+      <c r="A1241" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1241">
+        <v>2025</v>
+      </c>
+      <c r="C1241">
+        <v>0</v>
+      </c>
+      <c r="D1241">
+        <v>0</v>
+      </c>
+      <c r="E1241">
+        <v>0</v>
+      </c>
+      <c r="F1241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:6">
+      <c r="A1242" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1242">
+        <v>2026</v>
+      </c>
+      <c r="C1242">
+        <v>0</v>
+      </c>
+      <c r="D1242">
+        <v>0</v>
+      </c>
+      <c r="E1242">
+        <v>0</v>
+      </c>
+      <c r="F1242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:6">
+      <c r="A1243" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1243">
+        <v>2027</v>
+      </c>
+      <c r="C1243">
+        <v>0</v>
+      </c>
+      <c r="D1243">
+        <v>0</v>
+      </c>
+      <c r="E1243">
+        <v>0</v>
+      </c>
+      <c r="F1243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:6">
+      <c r="A1244" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1244">
+        <v>2028</v>
+      </c>
+      <c r="C1244">
+        <v>0</v>
+      </c>
+      <c r="D1244">
+        <v>0</v>
+      </c>
+      <c r="E1244">
+        <v>0</v>
+      </c>
+      <c r="F1244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:6">
+      <c r="A1245" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1245">
+        <v>2029</v>
+      </c>
+      <c r="C1245">
+        <v>0</v>
+      </c>
+      <c r="D1245">
+        <v>0</v>
+      </c>
+      <c r="E1245">
+        <v>0</v>
+      </c>
+      <c r="F1245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:6">
+      <c r="A1246" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1246">
+        <v>2030</v>
+      </c>
+      <c r="C1246">
+        <v>0</v>
+      </c>
+      <c r="D1246">
+        <v>0</v>
+      </c>
+      <c r="E1246">
+        <v>0</v>
+      </c>
+      <c r="F1246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:6">
+      <c r="A1247" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1247">
+        <v>2031</v>
+      </c>
+      <c r="C1247">
+        <v>0</v>
+      </c>
+      <c r="D1247">
+        <v>0</v>
+      </c>
+      <c r="E1247">
+        <v>0</v>
+      </c>
+      <c r="F1247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:6">
+      <c r="A1248" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1248">
+        <v>2032</v>
+      </c>
+      <c r="C1248">
+        <v>0</v>
+      </c>
+      <c r="D1248">
+        <v>0</v>
+      </c>
+      <c r="E1248">
+        <v>0</v>
+      </c>
+      <c r="F1248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:6">
+      <c r="A1249" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1249">
+        <v>2033</v>
+      </c>
+      <c r="C1249">
+        <v>0</v>
+      </c>
+      <c r="D1249">
+        <v>0</v>
+      </c>
+      <c r="E1249">
+        <v>0</v>
+      </c>
+      <c r="F1249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:6">
+      <c r="A1250" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1250">
+        <v>2034</v>
+      </c>
+      <c r="C1250">
+        <v>0</v>
+      </c>
+      <c r="D1250">
+        <v>0</v>
+      </c>
+      <c r="E1250">
+        <v>0</v>
+      </c>
+      <c r="F1250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:6">
+      <c r="A1251" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1251">
+        <v>2035</v>
+      </c>
+      <c r="C1251">
+        <v>0</v>
+      </c>
+      <c r="D1251">
+        <v>0</v>
+      </c>
+      <c r="E1251">
+        <v>0</v>
+      </c>
+      <c r="F1251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:6">
+      <c r="A1252" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1252">
+        <v>2036</v>
+      </c>
+      <c r="C1252">
+        <v>0</v>
+      </c>
+      <c r="D1252">
+        <v>0</v>
+      </c>
+      <c r="E1252">
+        <v>0</v>
+      </c>
+      <c r="F1252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:6">
+      <c r="A1253" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1253">
+        <v>2037</v>
+      </c>
+      <c r="C1253">
+        <v>0</v>
+      </c>
+      <c r="D1253">
+        <v>0</v>
+      </c>
+      <c r="E1253">
+        <v>0</v>
+      </c>
+      <c r="F1253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:6">
+      <c r="A1254" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1254">
+        <v>2038</v>
+      </c>
+      <c r="C1254">
+        <v>0</v>
+      </c>
+      <c r="D1254">
+        <v>0</v>
+      </c>
+      <c r="E1254">
+        <v>0</v>
+      </c>
+      <c r="F1254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:6">
+      <c r="A1255" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1255">
+        <v>2039</v>
+      </c>
+      <c r="C1255">
+        <v>0</v>
+      </c>
+      <c r="D1255">
+        <v>0</v>
+      </c>
+      <c r="E1255">
+        <v>0</v>
+      </c>
+      <c r="F1255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:6">
+      <c r="A1256" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1256">
+        <v>2040</v>
+      </c>
+      <c r="C1256">
+        <v>0</v>
+      </c>
+      <c r="D1256">
+        <v>0</v>
+      </c>
+      <c r="E1256">
+        <v>0</v>
+      </c>
+      <c r="F1256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:6">
+      <c r="A1257" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1257">
+        <v>2041</v>
+      </c>
+      <c r="C1257">
+        <v>0</v>
+      </c>
+      <c r="D1257">
+        <v>0</v>
+      </c>
+      <c r="E1257">
+        <v>0</v>
+      </c>
+      <c r="F1257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:6">
+      <c r="A1258" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1258">
+        <v>2042</v>
+      </c>
+      <c r="C1258">
+        <v>0</v>
+      </c>
+      <c r="D1258">
+        <v>0</v>
+      </c>
+      <c r="E1258">
+        <v>0</v>
+      </c>
+      <c r="F1258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:6">
+      <c r="A1259" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1259">
+        <v>2043</v>
+      </c>
+      <c r="C1259">
+        <v>0</v>
+      </c>
+      <c r="D1259">
+        <v>0</v>
+      </c>
+      <c r="E1259">
+        <v>0</v>
+      </c>
+      <c r="F1259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:6">
+      <c r="A1260" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1260">
+        <v>2044</v>
+      </c>
+      <c r="C1260">
+        <v>0</v>
+      </c>
+      <c r="D1260">
+        <v>0</v>
+      </c>
+      <c r="E1260">
+        <v>0</v>
+      </c>
+      <c r="F1260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:6">
+      <c r="A1261" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1261">
+        <v>2045</v>
+      </c>
+      <c r="C1261">
+        <v>0</v>
+      </c>
+      <c r="D1261">
+        <v>0</v>
+      </c>
+      <c r="E1261">
+        <v>0</v>
+      </c>
+      <c r="F1261">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
